--- a/Test_Cases/03_Add_Resource/Create_Test_Cases.xlsx
+++ b/Test_Cases/03_Add_Resource/Create_Test_Cases.xlsx
@@ -1,24 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Create Test Cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Create Test Cases'!$A$1:$K$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$36</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
+  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
+  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-15T16:05:34Z</dcterms:created>
+  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-15T16:05:34Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="2">
@@ -151,7 +147,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -434,7 +430,26 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Create Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Create Test Cases'!$A$1:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$36</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2624,7 +2639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2698,14 +2713,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2720,14 +2751,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2742,14 +2789,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2764,14 +2827,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2786,14 +2865,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2808,14 +2903,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2830,14 +2941,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2852,14 +2979,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2874,14 +3017,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Applicable - By Design</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (create.cy.js). The Create form Chapter/Topic field does not open a selector, BY DESIGN - the asset is always created against the current lesson topic, so the field is auto-filled and disabled like Grade &amp; Subject. These cases assume a browsing selector the product deliberately does not offer. TC-CREATE-014 covers the real behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2896,14 +3051,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Applicable - By Design</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (create.cy.js). The Create form Chapter/Topic field does not open a selector, BY DESIGN - the asset is always created against the current lesson topic, so the field is auto-filled and disabled like Grade &amp; Subject. These cases assume a browsing selector the product deliberately does not offer. TC-CREATE-014 covers the real behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2918,14 +3085,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Applicable - By Design</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (create.cy.js). The Create form Chapter/Topic field does not open a selector, BY DESIGN - the asset is always created against the current lesson topic, so the field is auto-filled and disabled like Grade &amp; Subject. These cases assume a browsing selector the product deliberately does not offer. TC-CREATE-014 covers the real behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2940,14 +3119,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Applicable - By Design</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (create.cy.js). The Create form Chapter/Topic field does not open a selector, BY DESIGN - the asset is always created against the current lesson topic, so the field is auto-filled and disabled like Grade &amp; Subject. These cases assume a browsing selector the product deliberately does not offer. TC-CREATE-014 covers the real behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2962,14 +3153,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Applicable - By Design</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (create.cy.js). The Create form Chapter/Topic field does not open a selector, BY DESIGN - the asset is always created against the current lesson topic, so the field is auto-filled and disabled like Grade &amp; Subject. These cases assume a browsing selector the product deliberately does not offer. TC-CREATE-014 covers the real behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2984,14 +3187,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3006,14 +3225,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3028,14 +3263,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3050,14 +3301,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3072,14 +3339,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3094,14 +3377,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3116,14 +3415,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3138,14 +3453,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3160,14 +3491,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3182,14 +3529,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3204,14 +3567,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3226,14 +3605,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3248,14 +3643,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3270,14 +3681,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3292,14 +3719,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3314,14 +3757,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Applicable - By Design</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (create.cy.js). The Create form Chapter/Topic field does not open a selector, BY DESIGN - the asset is always created against the current lesson topic, so the field is auto-filled and disabled like Grade &amp; Subject. These cases assume a browsing selector the product deliberately does not offer. TC-CREATE-014 covers the real behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3336,14 +3791,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3358,14 +3829,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3380,14 +3867,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Edit mode opened correctly and was populated, but no input[type=file] existed in the DOM, so the replacement file could not be attached.</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Not a product defect - test gap. In edit mode the current file is shown read-only and the file input only appears after the "Replace File" toggle is switched on; the test attached without toggling it. Fixed to toggle Replace File first and assert the input appears. Awaiting re-verification.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3402,14 +3905,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Edit mode opened correctly and was populated, but no input[type=file] existed in the DOM, so the replacement file could not be attached.</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Not a product defect - test gap. In edit mode the current file is shown read-only and the file input only appears after the "Replace File" toggle is switched on; the test attached without toggling it. Fixed to toggle Replace File first and assert the input appears. Awaiting re-verification.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3424,14 +3943,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3446,14 +3981,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/create.cy.js</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H36"/>
